--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008472363430969096</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>31679638</v>
+        <v>4173431</v>
       </c>
       <c r="L2" t="n">
-        <v>18075812</v>
+        <v>2058410</v>
       </c>
       <c r="M2" t="n">
-        <v>4328966</v>
+        <v>423068</v>
       </c>
       <c r="N2" t="n">
-        <v>212980</v>
+        <v>13597</v>
       </c>
       <c r="O2" t="n">
-        <v>2597033</v>
+        <v>259841</v>
       </c>
       <c r="P2" t="n">
-        <v>992451</v>
+        <v>103651</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999847412109375</v>
+        <v>0.9999589920043945</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8868862390518188</v>
+        <v>0.7965503931045532</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7766075730323792</v>
+        <v>0.6285935640335083</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7338212132453918</v>
+        <v>0.5383400917053223</v>
       </c>
       <c r="U2" t="n">
-        <v>0.316787451505661</v>
+        <v>0.1037099733948708</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7659653425216675</v>
+        <v>0.5882894992828369</v>
       </c>
       <c r="W2" t="n">
-        <v>0.85688716173172</v>
+        <v>0.721381664276123</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002030617636925397</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>31679638</v>
+        <v>4173431</v>
       </c>
       <c r="E3" t="n">
-        <v>3402236</v>
+        <v>800625</v>
       </c>
       <c r="F3" t="n">
-        <v>59553</v>
+        <v>21506</v>
       </c>
       <c r="G3" t="n">
-        <v>6296</v>
+        <v>2032</v>
       </c>
       <c r="H3" t="n">
-        <v>3381</v>
+        <v>1439</v>
       </c>
       <c r="I3" t="n">
-        <v>174</v>
+        <v>101</v>
       </c>
       <c r="J3" t="n">
-        <v>70115681</v>
+        <v>10016363</v>
       </c>
       <c r="K3" t="n">
-        <v>75115480</v>
+        <v>10264509</v>
       </c>
       <c r="L3" t="n">
-        <v>86219711</v>
+        <v>11825863</v>
       </c>
       <c r="M3" t="n">
-        <v>106204077</v>
+        <v>15030244</v>
       </c>
       <c r="N3" t="n">
-        <v>113223413</v>
+        <v>16122627</v>
       </c>
       <c r="O3" t="n">
-        <v>109947450</v>
+        <v>15637310</v>
       </c>
       <c r="P3" t="n">
-        <v>112787914</v>
+        <v>16096060</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.901236891746521</v>
+        <v>0.8348296284675598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7897522449493408</v>
+        <v>0.6261286735534668</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6626430153846741</v>
+        <v>0.4517307579517365</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3410654067993164</v>
+        <v>0.151982918381691</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7282257676124573</v>
+        <v>0.5090509653091431</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7332305312156677</v>
+        <v>0.5356447100639343</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03203040203446905</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>3803308</v>
+        <v>994345</v>
       </c>
       <c r="E4" t="n">
-        <v>18075812</v>
+        <v>2058410</v>
       </c>
       <c r="F4" t="n">
-        <v>883158</v>
+        <v>193391</v>
       </c>
       <c r="G4" t="n">
-        <v>47709</v>
+        <v>15460</v>
       </c>
       <c r="H4" t="n">
-        <v>72095</v>
+        <v>23599</v>
       </c>
       <c r="I4" t="n">
-        <v>5841</v>
+        <v>2300</v>
       </c>
       <c r="J4" t="n">
-        <v>673</v>
+        <v>259</v>
       </c>
       <c r="K4" t="n">
-        <v>4040431</v>
+        <v>1065950</v>
       </c>
       <c r="L4" t="n">
-        <v>5199536</v>
+        <v>1216218</v>
       </c>
       <c r="M4" t="n">
-        <v>1570245</v>
+        <v>362807</v>
       </c>
       <c r="N4" t="n">
-        <v>459332</v>
+        <v>117509</v>
       </c>
       <c r="O4" t="n">
-        <v>793503</v>
+        <v>181848</v>
       </c>
       <c r="P4" t="n">
-        <v>165754</v>
+        <v>40033</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999923706054688</v>
+        <v>0.9999794960021973</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8940039873123169</v>
+        <v>0.8152408599853516</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7831247448921204</v>
+        <v>0.6273587346076965</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6964181065559387</v>
+        <v>0.4912472367286682</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3284784257411957</v>
+        <v>0.1232896521687508</v>
       </c>
       <c r="V4" t="n">
-        <v>0.746618926525116</v>
+        <v>0.5458093881607056</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7902507185935974</v>
+        <v>0.6147910356521606</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>157719</v>
+        <v>51240</v>
       </c>
       <c r="E5" t="n">
-        <v>1516473</v>
+        <v>341080</v>
       </c>
       <c r="F5" t="n">
-        <v>4328966</v>
+        <v>423068</v>
       </c>
       <c r="G5" t="n">
-        <v>153362</v>
+        <v>36507</v>
       </c>
       <c r="H5" t="n">
-        <v>347770</v>
+        <v>75472</v>
       </c>
       <c r="I5" t="n">
-        <v>28544</v>
+        <v>9162</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3471651</v>
+        <v>825710</v>
       </c>
       <c r="L5" t="n">
-        <v>4812141</v>
+        <v>1229109</v>
       </c>
       <c r="M5" t="n">
-        <v>2203912</v>
+        <v>513481</v>
       </c>
       <c r="N5" t="n">
-        <v>411475</v>
+        <v>75867</v>
       </c>
       <c r="O5" t="n">
-        <v>969214</v>
+        <v>250601</v>
       </c>
       <c r="P5" t="n">
-        <v>361081</v>
+        <v>89856</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999940991401672</v>
+        <v>0.9999841451644897</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9342816472053528</v>
+        <v>0.8841575980186462</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9124143123626709</v>
+        <v>0.8502518534660339</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9669823050498962</v>
+        <v>0.9463374614715576</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9923818707466125</v>
+        <v>0.9881579279899597</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9845791459083557</v>
+        <v>0.9735174775123596</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9953910708427429</v>
+        <v>0.9920458197593689</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>74313</v>
+        <v>17211</v>
       </c>
       <c r="E6" t="n">
-        <v>144610</v>
+        <v>22892</v>
       </c>
       <c r="F6" t="n">
-        <v>129470</v>
+        <v>24689</v>
       </c>
       <c r="G6" t="n">
-        <v>212980</v>
+        <v>13597</v>
       </c>
       <c r="H6" t="n">
-        <v>58212</v>
+        <v>9836</v>
       </c>
       <c r="I6" t="n">
-        <v>4830</v>
+        <v>1227</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="D7" t="n">
-        <v>4894</v>
+        <v>3093</v>
       </c>
       <c r="E7" t="n">
-        <v>127794</v>
+        <v>47720</v>
       </c>
       <c r="F7" t="n">
-        <v>475329</v>
+        <v>114905</v>
       </c>
       <c r="G7" t="n">
-        <v>234671</v>
+        <v>57563</v>
       </c>
       <c r="H7" t="n">
-        <v>2597033</v>
+        <v>259841</v>
       </c>
       <c r="I7" t="n">
-        <v>126365</v>
+        <v>27243</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c r="D8" t="n">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>8423</v>
+        <v>3901</v>
       </c>
       <c r="F8" t="n">
-        <v>22735</v>
+        <v>8316</v>
       </c>
       <c r="G8" t="n">
-        <v>17294</v>
+        <v>5947</v>
       </c>
       <c r="H8" t="n">
-        <v>312045</v>
+        <v>71502</v>
       </c>
       <c r="I8" t="n">
-        <v>992451</v>
+        <v>103651</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
